--- a/players.xlsx
+++ b/players.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C23B92-AB76-4D5F-9B09-D1BA002CAF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544D327A-4743-44B5-A7EE-64B49041C4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hráči" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4085" uniqueCount="3272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="3333">
   <si>
     <t>id</t>
   </si>
@@ -9865,6 +9865,189 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1517290/unique-tournament/172/season/77019/statistics/overall</t>
+  </si>
+  <si>
+    <t>Zabransky</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/valentin-zabransky/profil/spieler/960455</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/cs/football/player/valentin-zabransky/1567317</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1567317</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1567317/unique-tournament/135/season/77531/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1567317/unique-tournament/135/season/77531/statistics/overall</t>
+  </si>
+  <si>
+    <t>Hakon</t>
+  </si>
+  <si>
+    <t>Volden</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/hakon-volden/profil/spieler/1126113</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/cs/football/player/hakon-volden/1486446</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1486446</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1486446/unique-tournament/20/season/70174/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1486446/unique-tournament/20/season/70174/statistics/overall</t>
+  </si>
+  <si>
+    <t>Oliwer</t>
+  </si>
+  <si>
+    <t>Szymoniak</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/oliwier-szymoniak/profil/spieler/1080744</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/oliwier-szymoniak/1885371</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1885371</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1885371/unique-tournament/229/season/77153/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1885371/unique-tournament/229/season/77153/statistics/overall</t>
+  </si>
+  <si>
+    <t>Gleb</t>
+  </si>
+  <si>
+    <t>Kuchko</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/gleb-kuchko/profil/spieler/981937</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/gleb-kuchko/1436340</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1436340</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1436340/unique-tournament/229/season/77153/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1436340/unique-tournament/229/season/77153/statistics/overall</t>
+  </si>
+  <si>
+    <t>Shina</t>
+  </si>
+  <si>
+    <t>Kumater</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/shina-kumater/profil/spieler/1331475</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/shina-kumater/1965286</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1965286</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1965286/unique-tournament/197/season/72074/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1965286/unique-tournament/197/season/72074/statistics/overall</t>
+  </si>
+  <si>
+    <t>Marc</t>
+  </si>
+  <si>
+    <t>Striednig</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/marc-striednig/profil/spieler/915419</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/marc-striednig/1385793</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385793</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385793/unique-tournament/135/season/77531/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385793/unique-tournament/135/season/77531/statistics/overall</t>
+  </si>
+  <si>
+    <t>Seydou</t>
+  </si>
+  <si>
+    <t>Diarra</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/seydou-diarra/profil/spieler/1230440</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/seydou-diarra/1889448</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1889448</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1889448/unique-tournament/135/season/77531/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1889448/unique-tournament/135/season/77531/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/dino-kojic/1893261</t>
+  </si>
+  <si>
+    <t>Taonsa</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/taonsa-axel/profil/spieler/1107314</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/taonsa-axel/1892815</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892815</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892815/unique-tournament/46/season/70171/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892815/unique-tournament/46/season/70171/statistics/overall</t>
+  </si>
+  <si>
+    <t>Kwiatkowski</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/oliwier-kwiatkowski/profil/spieler/1279298</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/oliwier-kwiatkowski/1892862</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892862</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892862/unique-tournament/229/season/77153/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1892862/unique-tournament/229/season/77153/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -9941,8 +10124,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J482" totalsRowShown="0">
-  <autoFilter ref="A1:J482" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J492" totalsRowShown="0">
+  <autoFilter ref="A1:J492" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10259,7 +10442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J482"/>
+  <dimension ref="A1:J492"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -24724,6 +24907,299 @@
       </c>
       <c r="J482" s="2" t="s">
         <v>3234</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A483">
+        <v>635</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C483" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D483" t="s">
+        <v>21</v>
+      </c>
+      <c r="F483" s="2" t="s">
+        <v>3273</v>
+      </c>
+      <c r="G483" s="2" t="s">
+        <v>3274</v>
+      </c>
+      <c r="H483" s="2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="I483" s="2" t="s">
+        <v>3276</v>
+      </c>
+      <c r="J483" s="2" t="s">
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A484">
+        <v>636</v>
+      </c>
+      <c r="B484" t="s">
+        <v>3278</v>
+      </c>
+      <c r="C484" t="s">
+        <v>3279</v>
+      </c>
+      <c r="D484" t="s">
+        <v>21</v>
+      </c>
+      <c r="F484" s="2" t="s">
+        <v>3280</v>
+      </c>
+      <c r="G484" s="2" t="s">
+        <v>3281</v>
+      </c>
+      <c r="H484" s="2" t="s">
+        <v>3282</v>
+      </c>
+      <c r="I484" s="2" t="s">
+        <v>3283</v>
+      </c>
+      <c r="J484" s="2" t="s">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A485">
+        <v>637</v>
+      </c>
+      <c r="B485" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C485" t="s">
+        <v>3286</v>
+      </c>
+      <c r="D485" t="s">
+        <v>20</v>
+      </c>
+      <c r="F485" s="2" t="s">
+        <v>3287</v>
+      </c>
+      <c r="G485" s="2" t="s">
+        <v>3288</v>
+      </c>
+      <c r="H485" s="2" t="s">
+        <v>3289</v>
+      </c>
+      <c r="I485" s="2" t="s">
+        <v>3290</v>
+      </c>
+      <c r="J485" s="2" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A486">
+        <v>638</v>
+      </c>
+      <c r="B486" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C486" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D486" t="s">
+        <v>20</v>
+      </c>
+      <c r="F486" s="2" t="s">
+        <v>3294</v>
+      </c>
+      <c r="G486" s="2" t="s">
+        <v>3295</v>
+      </c>
+      <c r="H486" s="2" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I486" s="2" t="s">
+        <v>3297</v>
+      </c>
+      <c r="J486" s="2" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A487">
+        <v>639</v>
+      </c>
+      <c r="B487" t="s">
+        <v>3299</v>
+      </c>
+      <c r="C487" t="s">
+        <v>3300</v>
+      </c>
+      <c r="D487" t="s">
+        <v>20</v>
+      </c>
+      <c r="F487" s="2" t="s">
+        <v>3301</v>
+      </c>
+      <c r="G487" s="2" t="s">
+        <v>3302</v>
+      </c>
+      <c r="H487" s="2" t="s">
+        <v>3303</v>
+      </c>
+      <c r="I487" s="2" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J487" s="2" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A488">
+        <v>640</v>
+      </c>
+      <c r="B488" t="s">
+        <v>3306</v>
+      </c>
+      <c r="C488" t="s">
+        <v>3307</v>
+      </c>
+      <c r="D488" t="s">
+        <v>18</v>
+      </c>
+      <c r="E488" t="s">
+        <v>28</v>
+      </c>
+      <c r="F488" s="2" t="s">
+        <v>3308</v>
+      </c>
+      <c r="G488" s="2" t="s">
+        <v>3309</v>
+      </c>
+      <c r="H488" s="2" t="s">
+        <v>3310</v>
+      </c>
+      <c r="I488" s="2" t="s">
+        <v>3311</v>
+      </c>
+      <c r="J488" s="2" t="s">
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A489">
+        <v>641</v>
+      </c>
+      <c r="B489" t="s">
+        <v>3313</v>
+      </c>
+      <c r="C489" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D489" t="s">
+        <v>32</v>
+      </c>
+      <c r="F489" s="2" t="s">
+        <v>3315</v>
+      </c>
+      <c r="G489" s="2" t="s">
+        <v>3316</v>
+      </c>
+      <c r="H489" s="2" t="s">
+        <v>3317</v>
+      </c>
+      <c r="I489" s="2" t="s">
+        <v>3318</v>
+      </c>
+      <c r="J489" s="2" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A490">
+        <v>642</v>
+      </c>
+      <c r="B490" t="s">
+        <v>870</v>
+      </c>
+      <c r="C490" t="s">
+        <v>871</v>
+      </c>
+      <c r="D490" t="s">
+        <v>127</v>
+      </c>
+      <c r="F490" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="G490" s="2" t="s">
+        <v>3320</v>
+      </c>
+      <c r="H490" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I490" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J490" s="2" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A491">
+        <v>643</v>
+      </c>
+      <c r="B491" t="s">
+        <v>770</v>
+      </c>
+      <c r="C491" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D491" t="s">
+        <v>6</v>
+      </c>
+      <c r="F491" s="2" t="s">
+        <v>3322</v>
+      </c>
+      <c r="G491" s="2" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H491" s="2" t="s">
+        <v>3324</v>
+      </c>
+      <c r="I491" s="2" t="s">
+        <v>3325</v>
+      </c>
+      <c r="J491" s="2" t="s">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A492">
+        <v>644</v>
+      </c>
+      <c r="B492" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C492" t="s">
+        <v>3327</v>
+      </c>
+      <c r="D492" t="s">
+        <v>32</v>
+      </c>
+      <c r="F492" s="2" t="s">
+        <v>3328</v>
+      </c>
+      <c r="G492" s="2" t="s">
+        <v>3329</v>
+      </c>
+      <c r="H492" s="2" t="s">
+        <v>3330</v>
+      </c>
+      <c r="I492" s="2" t="s">
+        <v>3331</v>
+      </c>
+      <c r="J492" s="2" t="s">
+        <v>3332</v>
       </c>
     </row>
   </sheetData>
@@ -26865,11 +27341,61 @@
     <hyperlink ref="J467" r:id="rId2134" xr:uid="{60214D98-35D1-4D98-8C5D-A414F24D3AC3}"/>
     <hyperlink ref="I469" r:id="rId2135" xr:uid="{1AD18F98-154F-46CB-963E-39061D01BBDC}"/>
     <hyperlink ref="J469" r:id="rId2136" xr:uid="{160DC526-8345-4108-9B24-A7BC7C12928D}"/>
+    <hyperlink ref="F483" r:id="rId2137" xr:uid="{85DC71B7-C2C4-49E8-86CE-7F2500BB789B}"/>
+    <hyperlink ref="G483" r:id="rId2138" xr:uid="{5A3CE7F0-7B38-48E6-A0B9-FCE9A75F9B53}"/>
+    <hyperlink ref="H483" r:id="rId2139" xr:uid="{2E8E84CE-4595-42DA-A27D-40698B9BE333}"/>
+    <hyperlink ref="I483" r:id="rId2140" xr:uid="{6ADD7929-F373-4CA9-AFFA-06DD76F99D6E}"/>
+    <hyperlink ref="J483" r:id="rId2141" xr:uid="{C5075E54-E364-452C-983F-469B5E949588}"/>
+    <hyperlink ref="F484" r:id="rId2142" xr:uid="{EDBF884B-5E35-4E96-B9C0-D5E92EB25CE5}"/>
+    <hyperlink ref="G484" r:id="rId2143" xr:uid="{B9BED4E4-20C6-45F6-B334-690E4AA9B777}"/>
+    <hyperlink ref="H484" r:id="rId2144" xr:uid="{1E2387F7-551B-453A-8392-05631802E5C8}"/>
+    <hyperlink ref="I484" r:id="rId2145" xr:uid="{57C9FA0D-4DFE-4EF9-ADA0-AFE73DDD5EE3}"/>
+    <hyperlink ref="J484" r:id="rId2146" xr:uid="{E30C2551-9C6F-44FE-A614-7D1E7E224041}"/>
+    <hyperlink ref="F485" r:id="rId2147" xr:uid="{34B8DCED-AEC9-4326-B8DD-18888341D742}"/>
+    <hyperlink ref="G485" r:id="rId2148" xr:uid="{A8C28441-05BE-4D63-93D4-482AD9F203B6}"/>
+    <hyperlink ref="H485" r:id="rId2149" xr:uid="{4AF82364-841E-4456-A4CC-1E8C72BC734F}"/>
+    <hyperlink ref="I485" r:id="rId2150" xr:uid="{A005D17D-7ED9-4611-AAEE-4F6DD9F69B64}"/>
+    <hyperlink ref="J485" r:id="rId2151" xr:uid="{5005EFE7-07CE-46E7-BF22-EC79253F4A91}"/>
+    <hyperlink ref="F486" r:id="rId2152" xr:uid="{AB5D9C37-47D2-4232-B2E6-0DD4EB699C18}"/>
+    <hyperlink ref="G486" r:id="rId2153" xr:uid="{785B3A79-B694-4042-9F8F-FD1305AC6343}"/>
+    <hyperlink ref="H486" r:id="rId2154" xr:uid="{7C8A7B9C-5C44-4EE6-8B4D-07FF9E0BFC45}"/>
+    <hyperlink ref="I486" r:id="rId2155" xr:uid="{3533839B-353E-4A52-8C1D-FCD1DB876499}"/>
+    <hyperlink ref="J486" r:id="rId2156" xr:uid="{5EED0716-AC9E-4B84-8DB1-E9526135E866}"/>
+    <hyperlink ref="F487" r:id="rId2157" xr:uid="{14A43222-8BCA-4529-8015-F7AB4C30DFC9}"/>
+    <hyperlink ref="G487" r:id="rId2158" xr:uid="{10B547D5-A4CB-461E-B571-80508A3A1A81}"/>
+    <hyperlink ref="H487" r:id="rId2159" xr:uid="{81EF6B0F-19EB-47B9-9ADF-C43C1AB1A402}"/>
+    <hyperlink ref="I487" r:id="rId2160" xr:uid="{368062BF-8FC2-4DB8-B90C-93B8EE3A3B0C}"/>
+    <hyperlink ref="J487" r:id="rId2161" xr:uid="{B67CB68D-93B0-444C-80F9-D069D3F82AC6}"/>
+    <hyperlink ref="F488" r:id="rId2162" xr:uid="{1DCFD493-E72C-48CE-8C4C-7708B958B29A}"/>
+    <hyperlink ref="G488" r:id="rId2163" xr:uid="{97002C80-89F2-42BB-AA1F-DC5ABF7DA175}"/>
+    <hyperlink ref="H488" r:id="rId2164" xr:uid="{2A46B126-7371-404D-A2A6-F75C9D391A07}"/>
+    <hyperlink ref="I488" r:id="rId2165" xr:uid="{5275B558-61D2-4BFC-B3B8-A5DE083CE333}"/>
+    <hyperlink ref="J488" r:id="rId2166" xr:uid="{36F97245-C8E1-4D2F-A842-EB7A320343AF}"/>
+    <hyperlink ref="F489" r:id="rId2167" xr:uid="{D87ED259-AFF4-40D6-BCCC-5EA02791192C}"/>
+    <hyperlink ref="G489" r:id="rId2168" xr:uid="{94D7F2B2-77A6-44C6-A265-C16D0B1B7A56}"/>
+    <hyperlink ref="H489" r:id="rId2169" xr:uid="{8AAF9C4D-99D3-42AB-9DF2-6883BE70B7DB}"/>
+    <hyperlink ref="I489" r:id="rId2170" xr:uid="{23587FCA-498E-4B14-8CCB-4E58A9EC23C7}"/>
+    <hyperlink ref="J489" r:id="rId2171" xr:uid="{FC6F1EE0-8383-4337-9607-10AD98B1D29E}"/>
+    <hyperlink ref="F490" r:id="rId2172" xr:uid="{055BAA38-7086-46C1-AA0D-237EFEDBD410}"/>
+    <hyperlink ref="G490" r:id="rId2173" xr:uid="{4A2831D8-9993-4D2A-B316-C3937AFFA85B}"/>
+    <hyperlink ref="H490" r:id="rId2174" xr:uid="{0226A28F-E258-45F1-B550-E69340051E65}"/>
+    <hyperlink ref="I490" r:id="rId2175" xr:uid="{FDAEF2C5-8E43-4FD1-8BBD-051B2A56E195}"/>
+    <hyperlink ref="J490" r:id="rId2176" xr:uid="{E59C650E-C91C-41E0-9DC8-E9973D5F4EA6}"/>
+    <hyperlink ref="F491" r:id="rId2177" xr:uid="{11FF1763-6DDA-4ECF-8AF3-48D42B5A09F9}"/>
+    <hyperlink ref="G491" r:id="rId2178" xr:uid="{D91F04C2-F651-4AF5-A290-510AFDD1AD5B}"/>
+    <hyperlink ref="H491" r:id="rId2179" xr:uid="{8DFB9F0E-F84E-441D-8671-350EEC46472F}"/>
+    <hyperlink ref="I491" r:id="rId2180" xr:uid="{B728D156-8031-48B0-98C6-4ABE79D69599}"/>
+    <hyperlink ref="J491" r:id="rId2181" xr:uid="{CBA48F11-3E4B-4984-8A04-FBBD9CC2AB95}"/>
+    <hyperlink ref="F492" r:id="rId2182" xr:uid="{A8437963-93A5-43EB-AA85-0745BCEF7464}"/>
+    <hyperlink ref="G492" r:id="rId2183" xr:uid="{1B02C1D1-E544-4F28-8834-FC1C885E554C}"/>
+    <hyperlink ref="H492" r:id="rId2184" xr:uid="{B7B40AE0-9343-4F8F-9B95-F80C83F4B18E}"/>
+    <hyperlink ref="I492" r:id="rId2185" xr:uid="{D5AF7DB8-F95E-4F25-A939-A99B96DF3B78}"/>
+    <hyperlink ref="J492" r:id="rId2186" xr:uid="{6E0306D0-980C-4A21-B727-3472159CDEF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2137"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2187"/>
   <tableParts count="1">
-    <tablePart r:id="rId2138"/>
+    <tablePart r:id="rId2188"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544D327A-4743-44B5-A7EE-64B49041C4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165EBC6B-2A99-4E61-9013-FDA84B270E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hráči" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="3333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4180" uniqueCount="3344">
   <si>
     <t>id</t>
   </si>
@@ -10048,6 +10048,39 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1892862/unique-tournament/229/season/77153/statistics/overall</t>
+  </si>
+  <si>
+    <t>Tatu</t>
+  </si>
+  <si>
+    <t>Hukkanen</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/tatu-hukkanen/profil/spieler/1120423</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/tatu-hukkanen/1641254</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1641254</t>
+  </si>
+  <si>
+    <t>Deket</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/matej-deket/profil/spieler/1141857</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/matej-deket/1990925</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1990925</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1990925/unique-tournament/222/season/77355/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1990925/unique-tournament/222/season/77355/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10124,8 +10157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J492" totalsRowShown="0">
-  <autoFilter ref="A1:J492" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J494" totalsRowShown="0">
+  <autoFilter ref="A1:J494" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10442,7 +10475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J492"/>
+  <dimension ref="A1:J494"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -25200,6 +25233,60 @@
       </c>
       <c r="J492" s="2" t="s">
         <v>3332</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A493">
+        <v>645</v>
+      </c>
+      <c r="B493" t="s">
+        <v>3333</v>
+      </c>
+      <c r="C493" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D493" t="s">
+        <v>21</v>
+      </c>
+      <c r="F493" s="2" t="s">
+        <v>3335</v>
+      </c>
+      <c r="G493" s="2" t="s">
+        <v>3336</v>
+      </c>
+      <c r="H493" s="2" t="s">
+        <v>3337</v>
+      </c>
+      <c r="I493" s="2"/>
+      <c r="J493" s="2"/>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A494">
+        <v>646</v>
+      </c>
+      <c r="B494" t="s">
+        <v>122</v>
+      </c>
+      <c r="C494" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D494" t="s">
+        <v>10</v>
+      </c>
+      <c r="F494" s="2" t="s">
+        <v>3339</v>
+      </c>
+      <c r="G494" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="H494" s="2" t="s">
+        <v>3341</v>
+      </c>
+      <c r="I494" s="2" t="s">
+        <v>3342</v>
+      </c>
+      <c r="J494" s="2" t="s">
+        <v>3343</v>
       </c>
     </row>
   </sheetData>
@@ -27391,11 +27478,19 @@
     <hyperlink ref="H492" r:id="rId2184" xr:uid="{B7B40AE0-9343-4F8F-9B95-F80C83F4B18E}"/>
     <hyperlink ref="I492" r:id="rId2185" xr:uid="{D5AF7DB8-F95E-4F25-A939-A99B96DF3B78}"/>
     <hyperlink ref="J492" r:id="rId2186" xr:uid="{6E0306D0-980C-4A21-B727-3472159CDEF3}"/>
+    <hyperlink ref="F493" r:id="rId2187" xr:uid="{EF1A4583-2E7D-40BB-884E-B408D1A95CBD}"/>
+    <hyperlink ref="G493" r:id="rId2188" xr:uid="{57E8C33E-38AB-405C-9AB8-7E98F9366DBD}"/>
+    <hyperlink ref="H493" r:id="rId2189" xr:uid="{2930D6E9-28A1-4923-902A-E2D0A27C1766}"/>
+    <hyperlink ref="F494" r:id="rId2190" xr:uid="{0167D3F6-F49A-4216-83CC-C8CFB2CB8064}"/>
+    <hyperlink ref="G494" r:id="rId2191" xr:uid="{CA048F0A-BA59-4E41-8D35-2BDFDB20CA25}"/>
+    <hyperlink ref="H494" r:id="rId2192" xr:uid="{043C858C-CA6A-4AE0-B8E2-EC6F1A06160E}"/>
+    <hyperlink ref="I494" r:id="rId2193" xr:uid="{845D72EE-0C22-4CAE-80CF-DC6A7A549913}"/>
+    <hyperlink ref="J494" r:id="rId2194" xr:uid="{ECBCDA32-561B-4D6E-AB74-62496F315560}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2187"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2195"/>
   <tableParts count="1">
-    <tablePart r:id="rId2188"/>
+    <tablePart r:id="rId2196"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B06F4D-234B-4209-8095-A9DEEEE7BD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CCF5B5-580A-4999-BE93-2E9DAFAD7CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4150" uniqueCount="3311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4242" uniqueCount="3383">
   <si>
     <t>id</t>
   </si>
@@ -9982,6 +9982,222 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/2268394/unique-tournament/215/season/77152/statistics/overall</t>
+  </si>
+  <si>
+    <t>Hussaini</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/hussaini-ibrahim/profil/spieler/1289275</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/hussaini-ibrahim/1940914</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1940914/unique-tournament/197/season/89428/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1940914</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1940914/unique-tournament/197/season/89428/statistics/overall</t>
+  </si>
+  <si>
+    <t>Kristian</t>
+  </si>
+  <si>
+    <t>Lonebu</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/kristian-lonebu/profil/spieler/1130922</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/kristian-lonebu/1845468</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1845468</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1845468/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1845468/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Jerdea</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/robert-jerdea/profil/spieler/887373</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/jerdea-robert-dumitru/1112607</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1112607</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1112607/unique-tournament/562/season/79020/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1112607/unique-tournament/562/season/79020/statistics/overall</t>
+  </si>
+  <si>
+    <t>Modou</t>
+  </si>
+  <si>
+    <t>Saidy</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/modou-saidy/profil/spieler/1378006</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/modou-saidy/1963023</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963023</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963023/unique-tournament/197/season/89428/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963023/unique-tournament/197/season/89428/statistics/overall</t>
+  </si>
+  <si>
+    <t>Baraitaru</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/mario-baraitaru/profil/spieler/1170516</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/mario-baraitaru/1907290</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1907290</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1907290/unique-tournament/562/season/79020/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1907290/unique-tournament/562/season/79020/statistics/overall</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>Tytens</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/renzo-tytens/profil/spieler/775982</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/renzo-tytens/1385527</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385527</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385527/unique-tournament/47/season/77031/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1385527/unique-tournament/47/season/77031/statistics/overall</t>
+  </si>
+  <si>
+    <t>Wilfinger</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/fabian-wilfinger/profil/spieler/1009490</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/fabian-wilfinger/1384232</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1384232</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1384232/unique-tournament/45/season/77382/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1384232/unique-tournament/45/season/77382/statistics/overall</t>
+  </si>
+  <si>
+    <t>Diogo</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/diogo-silva/profil/spieler/1116542</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/diogo-antonio-rodrigues-da-silva/1631803</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1631803</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1631803/unique-tournament/187/season/76944/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1631803/unique-tournament/187/season/76944/statistics/overall</t>
+  </si>
+  <si>
+    <t>Joao</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/joao-victor/profil/spieler/842370</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/joao-victor/1117051</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1117051</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1117051/unique-tournament/187/season/76944/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1117051/unique-tournament/187/season/76944/statistics/overall</t>
+  </si>
+  <si>
+    <t>Mladen</t>
+  </si>
+  <si>
+    <t>Jurkas</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/mladen-jurkas/profil/spieler/952692</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/mladen-jurkas/1587186</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1587186</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1587186/unique-tournament/222/season/77355/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1587186/unique-tournament/222/season/77355/statistics/overall</t>
+  </si>
+  <si>
+    <t>Fallou</t>
+  </si>
+  <si>
+    <t>Faye</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/fallou-faye/profil/spieler/1317245</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/fallou-faye/1936205</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1936205</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1936205/unique-tournament/212/season/77283/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1936205/unique-tournament/212/season/77283/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10058,8 +10274,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J496" totalsRowShown="0">
-  <autoFilter ref="A1:J496" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J507" totalsRowShown="0">
+  <autoFilter ref="A1:J507" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10376,7 +10592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J496"/>
+  <dimension ref="A1:J507"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -10385,7 +10601,7 @@
     <col min="4" max="4" width="10.46484375" customWidth="1"/>
     <col min="5" max="5" width="12.53125" customWidth="1"/>
     <col min="6" max="6" width="21.33203125" customWidth="1"/>
-    <col min="7" max="7" width="72.796875" customWidth="1"/>
+    <col min="7" max="7" width="81.06640625" customWidth="1"/>
     <col min="8" max="8" width="49.19921875" customWidth="1"/>
     <col min="9" max="9" width="90.33203125" customWidth="1"/>
     <col min="10" max="10" width="37.86328125" customWidth="1"/>
@@ -25156,6 +25372,337 @@
       </c>
       <c r="J496" s="2" t="s">
         <v>3310</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A497">
+        <v>649</v>
+      </c>
+      <c r="B497" t="s">
+        <v>3311</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D497" t="s">
+        <v>32</v>
+      </c>
+      <c r="E497" t="s">
+        <v>127</v>
+      </c>
+      <c r="F497" s="2" t="s">
+        <v>3312</v>
+      </c>
+      <c r="G497" s="2" t="s">
+        <v>3313</v>
+      </c>
+      <c r="H497" s="2" t="s">
+        <v>3315</v>
+      </c>
+      <c r="I497" s="2" t="s">
+        <v>3314</v>
+      </c>
+      <c r="J497" s="2" t="s">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A498">
+        <v>650</v>
+      </c>
+      <c r="B498" t="s">
+        <v>3317</v>
+      </c>
+      <c r="C498" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D498" t="s">
+        <v>10</v>
+      </c>
+      <c r="F498" s="2" t="s">
+        <v>3319</v>
+      </c>
+      <c r="G498" s="2" t="s">
+        <v>3320</v>
+      </c>
+      <c r="H498" s="2" t="s">
+        <v>3321</v>
+      </c>
+      <c r="I498" s="2" t="s">
+        <v>3322</v>
+      </c>
+      <c r="J498" s="2" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A499">
+        <v>651</v>
+      </c>
+      <c r="B499" t="s">
+        <v>3324</v>
+      </c>
+      <c r="C499" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D499" t="s">
+        <v>10</v>
+      </c>
+      <c r="F499" s="2" t="s">
+        <v>3326</v>
+      </c>
+      <c r="G499" s="2" t="s">
+        <v>3327</v>
+      </c>
+      <c r="H499" s="2" t="s">
+        <v>3328</v>
+      </c>
+      <c r="I499" s="2" t="s">
+        <v>3329</v>
+      </c>
+      <c r="J499" s="2" t="s">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A500">
+        <v>652</v>
+      </c>
+      <c r="B500" t="s">
+        <v>3331</v>
+      </c>
+      <c r="C500" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D500" t="s">
+        <v>127</v>
+      </c>
+      <c r="E500" t="s">
+        <v>10</v>
+      </c>
+      <c r="F500" s="2" t="s">
+        <v>3333</v>
+      </c>
+      <c r="G500" s="2" t="s">
+        <v>3334</v>
+      </c>
+      <c r="H500" s="2" t="s">
+        <v>3335</v>
+      </c>
+      <c r="I500" s="2" t="s">
+        <v>3336</v>
+      </c>
+      <c r="J500" s="2" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A501">
+        <v>653</v>
+      </c>
+      <c r="B501" t="s">
+        <v>348</v>
+      </c>
+      <c r="C501" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D501" t="s">
+        <v>21</v>
+      </c>
+      <c r="F501" s="2" t="s">
+        <v>3339</v>
+      </c>
+      <c r="G501" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="H501" s="2" t="s">
+        <v>3341</v>
+      </c>
+      <c r="I501" s="2" t="s">
+        <v>3342</v>
+      </c>
+      <c r="J501" s="2" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A502">
+        <v>654</v>
+      </c>
+      <c r="B502" t="s">
+        <v>3344</v>
+      </c>
+      <c r="C502" t="s">
+        <v>3345</v>
+      </c>
+      <c r="D502" t="s">
+        <v>20</v>
+      </c>
+      <c r="F502" s="2" t="s">
+        <v>3346</v>
+      </c>
+      <c r="G502" s="2" t="s">
+        <v>3347</v>
+      </c>
+      <c r="H502" s="2" t="s">
+        <v>3348</v>
+      </c>
+      <c r="I502" s="2" t="s">
+        <v>3349</v>
+      </c>
+      <c r="J502" s="2" t="s">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A503">
+        <v>655</v>
+      </c>
+      <c r="B503" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C503" t="s">
+        <v>3351</v>
+      </c>
+      <c r="D503" t="s">
+        <v>21</v>
+      </c>
+      <c r="F503" s="2" t="s">
+        <v>3352</v>
+      </c>
+      <c r="G503" s="2" t="s">
+        <v>3353</v>
+      </c>
+      <c r="H503" s="2" t="s">
+        <v>3354</v>
+      </c>
+      <c r="I503" s="2" t="s">
+        <v>3355</v>
+      </c>
+      <c r="J503" s="2" t="s">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A504">
+        <v>656</v>
+      </c>
+      <c r="B504" t="s">
+        <v>3357</v>
+      </c>
+      <c r="C504" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D504" t="s">
+        <v>21</v>
+      </c>
+      <c r="F504" s="2" t="s">
+        <v>3358</v>
+      </c>
+      <c r="G504" s="2" t="s">
+        <v>3359</v>
+      </c>
+      <c r="H504" s="2" t="s">
+        <v>3360</v>
+      </c>
+      <c r="I504" s="2" t="s">
+        <v>3361</v>
+      </c>
+      <c r="J504" s="2" t="s">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A505">
+        <v>657</v>
+      </c>
+      <c r="B505" t="s">
+        <v>3363</v>
+      </c>
+      <c r="C505" t="s">
+        <v>506</v>
+      </c>
+      <c r="D505" t="s">
+        <v>6</v>
+      </c>
+      <c r="E505" t="s">
+        <v>32</v>
+      </c>
+      <c r="F505" s="2" t="s">
+        <v>3364</v>
+      </c>
+      <c r="G505" s="2" t="s">
+        <v>3365</v>
+      </c>
+      <c r="H505" s="2" t="s">
+        <v>3366</v>
+      </c>
+      <c r="I505" s="2" t="s">
+        <v>3367</v>
+      </c>
+      <c r="J505" s="2" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A506">
+        <v>658</v>
+      </c>
+      <c r="B506" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C506" t="s">
+        <v>3377</v>
+      </c>
+      <c r="D506" t="s">
+        <v>18</v>
+      </c>
+      <c r="E506" t="s">
+        <v>28</v>
+      </c>
+      <c r="F506" s="2" t="s">
+        <v>3378</v>
+      </c>
+      <c r="G506" s="2" t="s">
+        <v>3379</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>3380</v>
+      </c>
+      <c r="I506" s="2" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J506" s="2" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A507">
+        <v>659</v>
+      </c>
+      <c r="B507" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C507" t="s">
+        <v>3370</v>
+      </c>
+      <c r="D507" t="s">
+        <v>100</v>
+      </c>
+      <c r="F507" s="2" t="s">
+        <v>3371</v>
+      </c>
+      <c r="G507" s="2" t="s">
+        <v>3372</v>
+      </c>
+      <c r="H507" s="2" t="s">
+        <v>3373</v>
+      </c>
+      <c r="I507" s="2" t="s">
+        <v>3374</v>
+      </c>
+      <c r="J507" s="2" t="s">
+        <v>3375</v>
       </c>
     </row>
   </sheetData>
@@ -27319,11 +27866,66 @@
     <hyperlink ref="H496" r:id="rId2156" xr:uid="{2F5A73CB-9FA7-4568-8D70-6244E348B203}"/>
     <hyperlink ref="I496" r:id="rId2157" xr:uid="{E0388BD6-0103-4AC2-9F46-CD32B275B11B}"/>
     <hyperlink ref="J496" r:id="rId2158" xr:uid="{5505B170-4A5F-4AFA-AEEC-F635C66138EA}"/>
+    <hyperlink ref="F497" r:id="rId2159" xr:uid="{11A514DE-4086-42CC-B231-726EFDCBB784}"/>
+    <hyperlink ref="G497" r:id="rId2160" xr:uid="{DE1C4A19-7DA8-4403-B3F8-05A1AB3A7434}"/>
+    <hyperlink ref="I497" r:id="rId2161" xr:uid="{0E81A7BC-8D65-43EF-956D-E23DAEE2AE01}"/>
+    <hyperlink ref="H497" r:id="rId2162" xr:uid="{7431FB14-94D2-4E44-BA8C-C90043F99608}"/>
+    <hyperlink ref="J497" r:id="rId2163" xr:uid="{048C90E5-C21B-413C-B9EA-10D31B9EFB9C}"/>
+    <hyperlink ref="F498" r:id="rId2164" xr:uid="{0D66E507-DD29-45DE-83A5-B04B895E3CC9}"/>
+    <hyperlink ref="G498" r:id="rId2165" xr:uid="{9EFD14DE-D55D-420B-B054-A6F09C544C77}"/>
+    <hyperlink ref="H498" r:id="rId2166" xr:uid="{DE6958CB-194A-4260-8B46-0C73F77D5DCE}"/>
+    <hyperlink ref="I498" r:id="rId2167" xr:uid="{7F5C8384-2A8E-4362-A9E3-8E659BC32601}"/>
+    <hyperlink ref="J498" r:id="rId2168" xr:uid="{EB392BAA-D029-4BB7-8EAD-1FF3672DBDBD}"/>
+    <hyperlink ref="F499" r:id="rId2169" xr:uid="{9439F884-F93E-429F-930E-A6D66B1195B1}"/>
+    <hyperlink ref="G499" r:id="rId2170" xr:uid="{833329FF-9407-4904-A47F-8811C597F3A7}"/>
+    <hyperlink ref="H499" r:id="rId2171" xr:uid="{4D4A3ECB-30B5-45D7-8C04-46B20E2B7CC0}"/>
+    <hyperlink ref="I499" r:id="rId2172" xr:uid="{42680EC2-4E29-4B5B-8097-4CFAE6DA7FEC}"/>
+    <hyperlink ref="J499" r:id="rId2173" xr:uid="{7D90749E-1E9B-4551-9EE3-59F82D75906A}"/>
+    <hyperlink ref="F500" r:id="rId2174" xr:uid="{B31E19AF-E3AE-4227-9771-F3766003A2D2}"/>
+    <hyperlink ref="G500" r:id="rId2175" xr:uid="{102AA8EC-06ED-4BE2-89ED-398FC5F42E0A}"/>
+    <hyperlink ref="H500" r:id="rId2176" xr:uid="{BEBA63BB-87F8-40C1-9E71-2A646A674364}"/>
+    <hyperlink ref="I500" r:id="rId2177" xr:uid="{2ABF9228-E09D-4C9A-BE5F-C7F71CBE278A}"/>
+    <hyperlink ref="J500" r:id="rId2178" xr:uid="{36294800-13BB-4742-B63C-E5C2AE0DCFE2}"/>
+    <hyperlink ref="F501" r:id="rId2179" xr:uid="{34017685-8825-4664-9E9F-45644A5A3281}"/>
+    <hyperlink ref="G501" r:id="rId2180" xr:uid="{3B135DE2-C8E5-41C7-9863-3951B30C7F17}"/>
+    <hyperlink ref="H501" r:id="rId2181" xr:uid="{44ACB2AF-F6FA-4214-96A4-C54687DD3F0B}"/>
+    <hyperlink ref="I501" r:id="rId2182" xr:uid="{74952C3D-7AE4-4874-8AB4-52C9D9016A30}"/>
+    <hyperlink ref="J501" r:id="rId2183" xr:uid="{BFC175E1-742C-4AB3-87FC-962E27E605AF}"/>
+    <hyperlink ref="F502" r:id="rId2184" xr:uid="{5978C5A1-F28A-4F63-9E65-CAA6F7CE4D02}"/>
+    <hyperlink ref="G502" r:id="rId2185" xr:uid="{161B686D-BEE9-4783-868E-C803B3E0F7D6}"/>
+    <hyperlink ref="H502" r:id="rId2186" xr:uid="{0C06DEF1-E5BB-4996-A4E5-19B5463C8190}"/>
+    <hyperlink ref="I502" r:id="rId2187" xr:uid="{4C0D2AB2-9970-4458-8281-9BB726F15705}"/>
+    <hyperlink ref="J502" r:id="rId2188" xr:uid="{00752205-AC1F-4529-8BA6-20E5954F5709}"/>
+    <hyperlink ref="F503" r:id="rId2189" xr:uid="{1EEB1103-E5E8-4833-81A5-A89360907894}"/>
+    <hyperlink ref="G503" r:id="rId2190" xr:uid="{7B81809B-F7DD-408A-B8FB-7CBEEA3E8D3B}"/>
+    <hyperlink ref="H503" r:id="rId2191" xr:uid="{5F7DD239-8D33-4D54-9F57-ADECB9BB4E69}"/>
+    <hyperlink ref="I503" r:id="rId2192" xr:uid="{4F12112F-F898-413D-8F36-3A3AEB654063}"/>
+    <hyperlink ref="J503" r:id="rId2193" xr:uid="{F2F2DB50-68AA-4F40-9FCC-511FEE070724}"/>
+    <hyperlink ref="F504" r:id="rId2194" xr:uid="{C57D2C8D-3176-4B5E-83B9-F2A12BC946A6}"/>
+    <hyperlink ref="G504" r:id="rId2195" xr:uid="{8867E262-C5A4-4B7F-98C5-04A5B607D9B4}"/>
+    <hyperlink ref="H504" r:id="rId2196" xr:uid="{9CD9B2E5-2426-4486-B602-7B537B0A09E8}"/>
+    <hyperlink ref="I504" r:id="rId2197" xr:uid="{9DF19EF7-AED9-44E0-8D99-EA690C387226}"/>
+    <hyperlink ref="J504" r:id="rId2198" xr:uid="{DF621F49-3DDC-4A03-AA24-9D1710D54F3F}"/>
+    <hyperlink ref="F505" r:id="rId2199" xr:uid="{379C81A1-955C-449E-B082-207E2727F257}"/>
+    <hyperlink ref="G505" r:id="rId2200" xr:uid="{5E02B38E-E8A7-4EFD-B662-DF59B79DC34D}"/>
+    <hyperlink ref="H505" r:id="rId2201" xr:uid="{BC8469C0-93FF-455A-BB9D-6337E292C2DB}"/>
+    <hyperlink ref="I505" r:id="rId2202" xr:uid="{EB3AC6C6-E330-4DB9-97E3-6D9E72F85AFD}"/>
+    <hyperlink ref="J505" r:id="rId2203" xr:uid="{DABB3C8E-27C7-4FEE-B006-B18973F7F178}"/>
+    <hyperlink ref="F507" r:id="rId2204" xr:uid="{5285F574-1E64-4AE9-AD23-973A60629C86}"/>
+    <hyperlink ref="G507" r:id="rId2205" xr:uid="{3ED29B09-4E7B-4F00-80A4-A8529EDA5158}"/>
+    <hyperlink ref="H507" r:id="rId2206" xr:uid="{DF26FEF6-D1E6-4B17-83B9-CC8B749D25E5}"/>
+    <hyperlink ref="I507" r:id="rId2207" xr:uid="{3171A958-3DA3-4DDE-8C1A-488A1ED098F9}"/>
+    <hyperlink ref="J507" r:id="rId2208" xr:uid="{4015427F-A95C-40BF-A6B2-7DE1C8CE9E12}"/>
+    <hyperlink ref="F506" r:id="rId2209" xr:uid="{FBC4F30A-A9B7-4A6F-9BCB-BD613DEE870C}"/>
+    <hyperlink ref="G506" r:id="rId2210" xr:uid="{5C77BF7C-3814-4D68-A93A-F26DE09D69DE}"/>
+    <hyperlink ref="H506" r:id="rId2211" xr:uid="{61325ED0-F70E-4F47-9705-939FA60E9565}"/>
+    <hyperlink ref="I506" r:id="rId2212" xr:uid="{F7F4F112-483B-48A3-858F-805BF72C08E1}"/>
+    <hyperlink ref="J506" r:id="rId2213" xr:uid="{54B8FE2D-FBAD-4668-A8AF-7C138465B05E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2159"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2214"/>
   <tableParts count="1">
-    <tablePart r:id="rId2160"/>
+    <tablePart r:id="rId2215"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CCF5B5-580A-4999-BE93-2E9DAFAD7CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5302548B-2C72-4D91-B018-1CCE1B363AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hráči" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4242" uniqueCount="3383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4259" uniqueCount="3396">
   <si>
     <t>id</t>
   </si>
@@ -10198,6 +10198,45 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1936205/unique-tournament/212/season/77283/statistics/overall</t>
+  </si>
+  <si>
+    <t>Toivo</t>
+  </si>
+  <si>
+    <t>Mero</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/toivo-mero/profil/spieler/1067927</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/toivo-mero/1542028</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542028</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542028/unique-tournament/41/season/87930/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542028/unique-tournament/41/season/87930/statistics/overall</t>
+  </si>
+  <si>
+    <t>Ezeh</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/david-ezeh/profil/spieler/937987</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/ezeh-david/1195777</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1195777</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1195777/unique-tournament/41/season/87930/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1195777/unique-tournament/41/season/87930/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10274,8 +10313,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J507" totalsRowShown="0">
-  <autoFilter ref="A1:J507" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J509" totalsRowShown="0">
+  <autoFilter ref="A1:J509" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10592,7 +10631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J507"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -25703,6 +25742,67 @@
       </c>
       <c r="J507" s="2" t="s">
         <v>3375</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A508">
+        <v>660</v>
+      </c>
+      <c r="B508" t="s">
+        <v>3383</v>
+      </c>
+      <c r="C508" t="s">
+        <v>3384</v>
+      </c>
+      <c r="D508" t="s">
+        <v>6</v>
+      </c>
+      <c r="E508" t="s">
+        <v>32</v>
+      </c>
+      <c r="F508" s="2" t="s">
+        <v>3385</v>
+      </c>
+      <c r="G508" s="2" t="s">
+        <v>3386</v>
+      </c>
+      <c r="H508" s="2" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I508" s="2" t="s">
+        <v>3388</v>
+      </c>
+      <c r="J508" s="2" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A509">
+        <v>661</v>
+      </c>
+      <c r="B509" t="s">
+        <v>328</v>
+      </c>
+      <c r="C509" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D509" t="s">
+        <v>10</v>
+      </c>
+      <c r="F509" s="2" t="s">
+        <v>3391</v>
+      </c>
+      <c r="G509" s="2" t="s">
+        <v>3392</v>
+      </c>
+      <c r="H509" s="2" t="s">
+        <v>3393</v>
+      </c>
+      <c r="I509" s="2" t="s">
+        <v>3394</v>
+      </c>
+      <c r="J509" s="2" t="s">
+        <v>3395</v>
       </c>
     </row>
   </sheetData>
@@ -27921,11 +28021,21 @@
     <hyperlink ref="H506" r:id="rId2211" xr:uid="{61325ED0-F70E-4F47-9705-939FA60E9565}"/>
     <hyperlink ref="I506" r:id="rId2212" xr:uid="{F7F4F112-483B-48A3-858F-805BF72C08E1}"/>
     <hyperlink ref="J506" r:id="rId2213" xr:uid="{54B8FE2D-FBAD-4668-A8AF-7C138465B05E}"/>
+    <hyperlink ref="F508" r:id="rId2214" xr:uid="{AEF7BB3F-8384-4BCD-B90F-972428E598B3}"/>
+    <hyperlink ref="G508" r:id="rId2215" xr:uid="{138E29EC-AE34-4DD2-B09C-1C04B96B0ACD}"/>
+    <hyperlink ref="H508" r:id="rId2216" xr:uid="{E251F615-A6AF-4420-BB4D-9B8572EC71DF}"/>
+    <hyperlink ref="I508" r:id="rId2217" xr:uid="{1434DBDD-3877-4BC0-B718-AF3B630174EE}"/>
+    <hyperlink ref="J508" r:id="rId2218" xr:uid="{069A3752-F537-4DEF-8957-E6163BD21709}"/>
+    <hyperlink ref="F509" r:id="rId2219" xr:uid="{8095E4CE-B2CD-49DD-BFBC-A9D1D8FE6248}"/>
+    <hyperlink ref="G509" r:id="rId2220" xr:uid="{871345DF-016D-461E-A193-76B08F61DDA3}"/>
+    <hyperlink ref="H509" r:id="rId2221" xr:uid="{D81FBD0F-BF5F-432C-9A79-B13BA32072BE}"/>
+    <hyperlink ref="I509" r:id="rId2222" xr:uid="{AF5E8EF1-1C5E-43D4-96F8-859FAB85DDA7}"/>
+    <hyperlink ref="J509" r:id="rId2223" xr:uid="{777B0EF1-3611-45EC-B943-FEF597C9E5DD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2214"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2224"/>
   <tableParts count="1">
-    <tablePart r:id="rId2215"/>
+    <tablePart r:id="rId2225"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5302548B-2C72-4D91-B018-1CCE1B363AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EAF420-E784-4D21-9C77-5EA7E785B8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hráči" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4259" uniqueCount="3396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4309" uniqueCount="3436">
   <si>
     <t>id</t>
   </si>
@@ -10237,6 +10237,126 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1195777/unique-tournament/41/season/87930/statistics/overall</t>
+  </si>
+  <si>
+    <t>Ludwig</t>
+  </si>
+  <si>
+    <t>Arvidsson</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/ludvig-arvidsson/profil/spieler/1291830</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/erik-arvidsson/2040234</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2040234</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2040234/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2040234/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/abdoulaye-doumbia/profil/spieler/1519157</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/abdoulaye-doumbia/2011233</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2011233</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2011233/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2011233/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>Bo</t>
+  </si>
+  <si>
+    <t>Hegland</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/bo-hegland/profil/spieler/912072</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/bo-asulv-hegland/1200574</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1200574</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1200574/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1200574/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>Mamdou</t>
+  </si>
+  <si>
+    <t>Jalloh</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/mamadou-jalloh/profil/spieler/955508</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/mamadou-jalloh/1891181</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1891181</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1891181/unique-tournament/41/season/87930/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1891181/unique-tournament/41/season/87930/statistics/overall</t>
+  </si>
+  <si>
+    <t>Papa Omar</t>
+  </si>
+  <si>
+    <t>Gningue</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/papa-omar-gningue/profil/spieler/1521393</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/papa-omar-gningue/1963028</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963028</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963028/unique-tournament/197/season/89428/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1963028/unique-tournament/197/season/89428/statistics/overall</t>
+  </si>
+  <si>
+    <t>Iiro</t>
+  </si>
+  <si>
+    <t>Mendolin</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/iiro-mendolin/profil/spieler/927996</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/iiro-mendolin/1416537</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1416537</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1416537/unique-tournament/41/season/87930/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1416537/unique-tournament/41/season/87930/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10313,8 +10433,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J509" totalsRowShown="0">
-  <autoFilter ref="A1:J509" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J515" totalsRowShown="0">
+  <autoFilter ref="A1:J515" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10631,7 +10751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J515"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -25803,6 +25923,186 @@
       </c>
       <c r="J509" s="2" t="s">
         <v>3395</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A510">
+        <v>662</v>
+      </c>
+      <c r="B510" t="s">
+        <v>3396</v>
+      </c>
+      <c r="C510" t="s">
+        <v>3397</v>
+      </c>
+      <c r="D510" t="s">
+        <v>32</v>
+      </c>
+      <c r="F510" s="2" t="s">
+        <v>3398</v>
+      </c>
+      <c r="G510" s="2" t="s">
+        <v>3399</v>
+      </c>
+      <c r="H510" s="2" t="s">
+        <v>3400</v>
+      </c>
+      <c r="I510" s="2" t="s">
+        <v>3401</v>
+      </c>
+      <c r="J510" s="2" t="s">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A511">
+        <v>663</v>
+      </c>
+      <c r="B511" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C511" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D511" t="s">
+        <v>28</v>
+      </c>
+      <c r="E511" t="s">
+        <v>18</v>
+      </c>
+      <c r="F511" s="2" t="s">
+        <v>3403</v>
+      </c>
+      <c r="G511" s="2" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H511" s="2" t="s">
+        <v>3405</v>
+      </c>
+      <c r="I511" s="2" t="s">
+        <v>3406</v>
+      </c>
+      <c r="J511" s="2" t="s">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A512">
+        <v>664</v>
+      </c>
+      <c r="B512" t="s">
+        <v>3408</v>
+      </c>
+      <c r="C512" t="s">
+        <v>3409</v>
+      </c>
+      <c r="D512" t="s">
+        <v>10</v>
+      </c>
+      <c r="E512" t="s">
+        <v>127</v>
+      </c>
+      <c r="F512" s="2" t="s">
+        <v>3410</v>
+      </c>
+      <c r="G512" s="2" t="s">
+        <v>3411</v>
+      </c>
+      <c r="H512" s="2" t="s">
+        <v>3412</v>
+      </c>
+      <c r="I512" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="J512" s="2" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A513">
+        <v>665</v>
+      </c>
+      <c r="B513" t="s">
+        <v>3415</v>
+      </c>
+      <c r="C513" t="s">
+        <v>3416</v>
+      </c>
+      <c r="D513" t="s">
+        <v>100</v>
+      </c>
+      <c r="F513" s="2" t="s">
+        <v>3417</v>
+      </c>
+      <c r="G513" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="H513" s="2" t="s">
+        <v>3419</v>
+      </c>
+      <c r="I513" s="2" t="s">
+        <v>3420</v>
+      </c>
+      <c r="J513" s="2" t="s">
+        <v>3421</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A514">
+        <v>666</v>
+      </c>
+      <c r="B514" t="s">
+        <v>3422</v>
+      </c>
+      <c r="C514" t="s">
+        <v>3423</v>
+      </c>
+      <c r="D514" t="s">
+        <v>21</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>3424</v>
+      </c>
+      <c r="G514" s="2" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H514" s="2" t="s">
+        <v>3426</v>
+      </c>
+      <c r="I514" s="2" t="s">
+        <v>3427</v>
+      </c>
+      <c r="J514" s="2" t="s">
+        <v>3428</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A515">
+        <v>667</v>
+      </c>
+      <c r="B515" t="s">
+        <v>3429</v>
+      </c>
+      <c r="C515" t="s">
+        <v>3430</v>
+      </c>
+      <c r="D515" t="s">
+        <v>28</v>
+      </c>
+      <c r="F515" s="2" t="s">
+        <v>3431</v>
+      </c>
+      <c r="G515" s="2" t="s">
+        <v>3432</v>
+      </c>
+      <c r="H515" s="2" t="s">
+        <v>3433</v>
+      </c>
+      <c r="I515" s="2" t="s">
+        <v>3434</v>
+      </c>
+      <c r="J515" s="2" t="s">
+        <v>3435</v>
       </c>
     </row>
   </sheetData>
@@ -28031,11 +28331,41 @@
     <hyperlink ref="H509" r:id="rId2221" xr:uid="{D81FBD0F-BF5F-432C-9A79-B13BA32072BE}"/>
     <hyperlink ref="I509" r:id="rId2222" xr:uid="{AF5E8EF1-1C5E-43D4-96F8-859FAB85DDA7}"/>
     <hyperlink ref="J509" r:id="rId2223" xr:uid="{777B0EF1-3611-45EC-B943-FEF597C9E5DD}"/>
+    <hyperlink ref="F510" r:id="rId2224" xr:uid="{85722AFA-64F9-42A1-8F03-CC994E23733C}"/>
+    <hyperlink ref="G510" r:id="rId2225" xr:uid="{EC16184A-95A7-466C-9A52-E9FF54C5CD0E}"/>
+    <hyperlink ref="H510" r:id="rId2226" xr:uid="{9715AA7C-23F6-4611-A6E4-EA4C20301116}"/>
+    <hyperlink ref="I510" r:id="rId2227" xr:uid="{D975CE65-29EE-45E1-ABA1-5DD015887883}"/>
+    <hyperlink ref="J510" r:id="rId2228" xr:uid="{AF87D359-DDDD-4FA7-B5D3-1B0C52860B6E}"/>
+    <hyperlink ref="F511" r:id="rId2229" xr:uid="{51B21C4D-D429-4F28-A2F2-1299DAF99B24}"/>
+    <hyperlink ref="G511" r:id="rId2230" xr:uid="{8054B086-C56B-434F-B7AD-39FFD39309F1}"/>
+    <hyperlink ref="H511" r:id="rId2231" xr:uid="{2EFCBF27-7171-4C1B-8D21-50AA39434574}"/>
+    <hyperlink ref="I511" r:id="rId2232" xr:uid="{4E219486-1999-4EC5-B247-0B594801A944}"/>
+    <hyperlink ref="J511" r:id="rId2233" xr:uid="{91EB75D4-3557-4A40-A1A8-9993B1E21029}"/>
+    <hyperlink ref="F512" r:id="rId2234" xr:uid="{B6B556B9-0815-4EAC-A187-9B452DE01CFA}"/>
+    <hyperlink ref="G512" r:id="rId2235" xr:uid="{08956C81-F1B1-41CE-A4A1-29DF18CB51DE}"/>
+    <hyperlink ref="H512" r:id="rId2236" xr:uid="{E9A9F233-D6A2-4EEE-BEF1-71AC5D2F5FC0}"/>
+    <hyperlink ref="I512" r:id="rId2237" xr:uid="{2655C98A-42F7-4557-A559-6252F47B3146}"/>
+    <hyperlink ref="J512" r:id="rId2238" xr:uid="{AC514643-4E40-4C0D-9B15-862097E41BC5}"/>
+    <hyperlink ref="F513" r:id="rId2239" xr:uid="{25743FA8-B043-4DBF-B4CC-3693A6943E76}"/>
+    <hyperlink ref="G513" r:id="rId2240" xr:uid="{5FE03ADD-CBB8-49F7-93BB-F3D898B0C5DC}"/>
+    <hyperlink ref="H513" r:id="rId2241" xr:uid="{A71E3CE6-D6CE-4A6E-86D9-7E936F9BBA2F}"/>
+    <hyperlink ref="I513" r:id="rId2242" xr:uid="{3E9D4EC6-6F29-42A3-97FD-14F0B68FF0FA}"/>
+    <hyperlink ref="J513" r:id="rId2243" xr:uid="{ACA34423-31D1-496B-A4F1-BA7A121ED529}"/>
+    <hyperlink ref="F514" r:id="rId2244" xr:uid="{3A904E2C-AE0F-4704-A845-FFBF50715E05}"/>
+    <hyperlink ref="G514" r:id="rId2245" xr:uid="{14C73312-A6E4-4A5F-B7BD-59A756C95A96}"/>
+    <hyperlink ref="H514" r:id="rId2246" xr:uid="{E5CDA569-CD7D-445E-A780-230100EF668B}"/>
+    <hyperlink ref="I514" r:id="rId2247" xr:uid="{70160682-9291-455F-830C-40FFF0EB8F6F}"/>
+    <hyperlink ref="J514" r:id="rId2248" xr:uid="{F7316185-199E-4B4D-93FF-0B828D9C2212}"/>
+    <hyperlink ref="F515" r:id="rId2249" xr:uid="{7A4EA4DE-47DE-49FC-9BCB-8E5FBD03E829}"/>
+    <hyperlink ref="G515" r:id="rId2250" xr:uid="{76B7B77C-32ED-4803-AD02-659AEFDA42E5}"/>
+    <hyperlink ref="H515" r:id="rId2251" xr:uid="{71D9A00A-A7EA-4113-AA08-9D0F62F33BFC}"/>
+    <hyperlink ref="I515" r:id="rId2252" xr:uid="{A77C1B2D-8BAB-42CC-9223-A2A4BDE35C5C}"/>
+    <hyperlink ref="J515" r:id="rId2253" xr:uid="{FE1E735C-A74D-4E88-AAB7-62F46C1CE98F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2224"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2254"/>
   <tableParts count="1">
-    <tablePart r:id="rId2225"/>
+    <tablePart r:id="rId2255"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EAF420-E784-4D21-9C77-5EA7E785B8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C862B0-AB4D-485A-93A9-81F6C5E30E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4309" uniqueCount="3436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="3475">
   <si>
     <t>id</t>
   </si>
@@ -10357,6 +10357,123 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1416537/unique-tournament/41/season/87930/statistics/overall</t>
+  </si>
+  <si>
+    <t>Kurtovic</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/kenan-kurtovic/profil/spieler/960985</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/kenan-kurtovic/1924336</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1924336</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1924336/unique-tournament/212/season/77283/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1924336/unique-tournament/212/season/77283/statistics/overall</t>
+  </si>
+  <si>
+    <t>Rehuš</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/milan-rehus/profil/spieler/726662</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/milan-rehus/1150946</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1150946</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1150946/unique-tournament/211/season/77154/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1150946/unique-tournament/211/season/77154/statistics/overall</t>
+  </si>
+  <si>
+    <t>Mohamed-Amine</t>
+  </si>
+  <si>
+    <t>Bouchenna</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/mohamed-amine-bouchenna/profil/spieler/955360</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/mohamed-amine-bouchenna/1426226</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1426226</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1426226/unique-tournament/135/season/77531/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1426226/unique-tournament/135/season/77531/statistics/overall</t>
+  </si>
+  <si>
+    <t>Ensar</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/ensar-music/profil/spieler/980665</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/ensar-music/1566220</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1566220</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1566220/unique-tournament/135/season/77531/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1566220/unique-tournament/135/season/77531/statistics/overall</t>
+  </si>
+  <si>
+    <t>Alfred</t>
+  </si>
+  <si>
+    <t>Gøthler</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/alfred-gothler/profil/spieler/1140564</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/alfred-gothler/1586925</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1586925</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1586925/unique-tournament/47/season/77031/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1586925/unique-tournament/47/season/77031/statistics/overall</t>
+  </si>
+  <si>
+    <t>Nfansu</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/nfansu-njie/profil/spieler/1130251</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/njie-nfansu/1516150</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1516150</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1516150/unique-tournament/187/season/76944/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1516150/unique-tournament/187/season/76944/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10433,8 +10550,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J515" totalsRowShown="0">
-  <autoFilter ref="A1:J515" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J521" totalsRowShown="0">
+  <autoFilter ref="A1:J521" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10751,7 +10868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J515"/>
+  <dimension ref="A1:J521"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -26103,6 +26220,183 @@
       </c>
       <c r="J515" s="2" t="s">
         <v>3435</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A516">
+        <v>668</v>
+      </c>
+      <c r="B516" t="s">
+        <v>608</v>
+      </c>
+      <c r="C516" t="s">
+        <v>3436</v>
+      </c>
+      <c r="D516" t="s">
+        <v>10</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>3437</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>3438</v>
+      </c>
+      <c r="H516" s="2" t="s">
+        <v>3439</v>
+      </c>
+      <c r="I516" s="2" t="s">
+        <v>3440</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A517">
+        <v>669</v>
+      </c>
+      <c r="B517" t="s">
+        <v>728</v>
+      </c>
+      <c r="C517" t="s">
+        <v>3442</v>
+      </c>
+      <c r="D517" t="s">
+        <v>10</v>
+      </c>
+      <c r="E517" t="s">
+        <v>127</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>3443</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>3444</v>
+      </c>
+      <c r="H517" s="2" t="s">
+        <v>3445</v>
+      </c>
+      <c r="I517" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>3447</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A518">
+        <v>670</v>
+      </c>
+      <c r="B518" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C518" t="s">
+        <v>3449</v>
+      </c>
+      <c r="D518" t="s">
+        <v>127</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>3450</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>3451</v>
+      </c>
+      <c r="H518" s="2" t="s">
+        <v>3452</v>
+      </c>
+      <c r="I518" s="2" t="s">
+        <v>3453</v>
+      </c>
+      <c r="J518" s="2" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A519">
+        <v>671</v>
+      </c>
+      <c r="B519" t="s">
+        <v>3455</v>
+      </c>
+      <c r="C519" t="s">
+        <v>3456</v>
+      </c>
+      <c r="D519" t="s">
+        <v>127</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>3458</v>
+      </c>
+      <c r="H519" s="2" t="s">
+        <v>3459</v>
+      </c>
+      <c r="I519" s="2" t="s">
+        <v>3460</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A520">
+        <v>672</v>
+      </c>
+      <c r="B520" t="s">
+        <v>3462</v>
+      </c>
+      <c r="C520" t="s">
+        <v>3463</v>
+      </c>
+      <c r="D520" t="s">
+        <v>10</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>3464</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>3465</v>
+      </c>
+      <c r="H520" s="2" t="s">
+        <v>3466</v>
+      </c>
+      <c r="I520" s="2" t="s">
+        <v>3467</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A521">
+        <v>673</v>
+      </c>
+      <c r="B521" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C521" t="s">
+        <v>171</v>
+      </c>
+      <c r="D521" t="s">
+        <v>32</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>3470</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>3471</v>
+      </c>
+      <c r="H521" s="2" t="s">
+        <v>3472</v>
+      </c>
+      <c r="I521" s="2" t="s">
+        <v>3473</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>3474</v>
       </c>
     </row>
   </sheetData>
@@ -28361,11 +28655,41 @@
     <hyperlink ref="H515" r:id="rId2251" xr:uid="{71D9A00A-A7EA-4113-AA08-9D0F62F33BFC}"/>
     <hyperlink ref="I515" r:id="rId2252" xr:uid="{A77C1B2D-8BAB-42CC-9223-A2A4BDE35C5C}"/>
     <hyperlink ref="J515" r:id="rId2253" xr:uid="{FE1E735C-A74D-4E88-AAB7-62F46C1CE98F}"/>
+    <hyperlink ref="F516" r:id="rId2254" xr:uid="{07064E6E-2C48-4A7C-AB8D-2E0534EDB019}"/>
+    <hyperlink ref="G516" r:id="rId2255" xr:uid="{7B2566FC-C44E-4AA4-96F7-33ACE3DCAF39}"/>
+    <hyperlink ref="H516" r:id="rId2256" xr:uid="{96B7FBB0-E10F-4870-90DE-98B9EE15B4D2}"/>
+    <hyperlink ref="I516" r:id="rId2257" xr:uid="{DD265E98-D388-4629-BDC5-FC3EFDD62E82}"/>
+    <hyperlink ref="J516" r:id="rId2258" xr:uid="{7960EE60-8C9B-4C38-BCE3-3884592DDA07}"/>
+    <hyperlink ref="F517" r:id="rId2259" xr:uid="{894C4525-F1C7-4EB3-B332-9D6AFE98215F}"/>
+    <hyperlink ref="G517" r:id="rId2260" xr:uid="{1C6E27AB-EF25-4AC6-99A0-D6FD7D7A5807}"/>
+    <hyperlink ref="H517" r:id="rId2261" xr:uid="{5B32BD49-4796-4C63-904B-4B773D966DAB}"/>
+    <hyperlink ref="I517" r:id="rId2262" xr:uid="{01BD5481-AF91-4AF0-8483-C9A488B0F795}"/>
+    <hyperlink ref="J517" r:id="rId2263" xr:uid="{BC04E8F9-2EB0-4BAB-B3D8-C6C4502EDDE0}"/>
+    <hyperlink ref="F518" r:id="rId2264" xr:uid="{BF0698F9-3987-4B78-9F35-13A7B4FAAE14}"/>
+    <hyperlink ref="G518" r:id="rId2265" xr:uid="{EDBA6A1F-33A6-4F0A-8ED8-3CB7036F90D7}"/>
+    <hyperlink ref="H518" r:id="rId2266" xr:uid="{7FF3B45B-D465-4DDB-B897-383A1EC97745}"/>
+    <hyperlink ref="I518" r:id="rId2267" xr:uid="{71A7B980-A62E-44D6-85DC-F09B39C7B80C}"/>
+    <hyperlink ref="J518" r:id="rId2268" xr:uid="{645AE976-F96C-4A6E-AD66-ACB757DE94D5}"/>
+    <hyperlink ref="F519" r:id="rId2269" xr:uid="{E9776FC6-59C6-4E5E-ACEB-F7E7A8B67EE1}"/>
+    <hyperlink ref="G519" r:id="rId2270" xr:uid="{C1C0E065-8969-46B7-B2E0-302B407F0FF7}"/>
+    <hyperlink ref="H519" r:id="rId2271" xr:uid="{22812CCD-81BA-4314-9839-585757839832}"/>
+    <hyperlink ref="I519" r:id="rId2272" xr:uid="{B99CCA3C-026D-4508-8E52-9F045A7C1065}"/>
+    <hyperlink ref="J519" r:id="rId2273" xr:uid="{B8876445-0425-405D-818D-B750B74129FF}"/>
+    <hyperlink ref="F520" r:id="rId2274" xr:uid="{9D8D6116-C8C4-4EF6-9BA0-E1DC1C6FDE5E}"/>
+    <hyperlink ref="G520" r:id="rId2275" xr:uid="{C68064F8-9710-49D9-9F63-5A2BCCD14F33}"/>
+    <hyperlink ref="H520" r:id="rId2276" xr:uid="{56FB2FB2-8583-4C23-8721-55F84999F5D6}"/>
+    <hyperlink ref="I520" r:id="rId2277" xr:uid="{C8C467B4-5867-4ADF-A221-62DE93A22183}"/>
+    <hyperlink ref="J520" r:id="rId2278" xr:uid="{98B7261E-998A-4729-9B9F-ECAD16748EC7}"/>
+    <hyperlink ref="F521" r:id="rId2279" xr:uid="{1E06C27E-5F86-43BA-B3A3-CFC814CE8D2D}"/>
+    <hyperlink ref="G521" r:id="rId2280" xr:uid="{6974F645-1E29-4393-AB7A-4E8EE27A3732}"/>
+    <hyperlink ref="H521" r:id="rId2281" xr:uid="{FDB8B5EE-9686-443B-9CBD-875139726FFD}"/>
+    <hyperlink ref="I521" r:id="rId2282" xr:uid="{60E642AA-04E8-4752-B0CD-699CC1C92B30}"/>
+    <hyperlink ref="J521" r:id="rId2283" xr:uid="{12DD4329-0B4E-41AA-B7A1-C95725498A3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2254"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2284"/>
   <tableParts count="1">
-    <tablePart r:id="rId2255"/>
+    <tablePart r:id="rId2285"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C862B0-AB4D-485A-93A9-81F6C5E30E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676533F5-9CB7-47EF-B0B9-979C2D5967F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="3475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4467" uniqueCount="3572">
   <si>
     <t>id</t>
   </si>
@@ -10474,6 +10474,297 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1516150/unique-tournament/187/season/76944/statistics/overall</t>
+  </si>
+  <si>
+    <t>Laegreid</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/julian-laegreid/profil/spieler/1069171</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/julian-laegreid/1931534</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1931534</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1931534/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1931534/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>Josué</t>
+  </si>
+  <si>
+    <t>Vergara</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/josue-vergara/profil/spieler/1291709</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/josue-vergara/1916618</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1916618</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1916618/unique-tournament/197/season/89428/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1916618/unique-tournament/197/season/89428/statistics/overall</t>
+  </si>
+  <si>
+    <t>Skiba</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/dominik-skiba/profil/spieler/1211963</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/dominik-skiba/2439796</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2439796</t>
+  </si>
+  <si>
+    <t>Mensah</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/emmanuel-mensah/profil/spieler/1063914</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/emmanuel-mensah/1457094</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1457094</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1457094/unique-tournament/562/season/79020/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1457094/unique-tournament/562/season/79020/statistics/overall</t>
+  </si>
+  <si>
+    <t>Goodlad</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/gideon-goodlad/profil/spieler/1283034</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/gideon-uche-goodlad/1899419</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1899419</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1899419/unique-tournament/562/season/79020/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1899419/unique-tournament/562/season/79020/statistics/overall</t>
+  </si>
+  <si>
+    <t>Kupijbida</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/mikkel-kupijbida/profil/spieler/1274379</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/mikkel-kupijbida/2219589</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2219589</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2219589/unique-tournament/47/season/77031/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2219589/unique-tournament/47/season/77031/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1125356/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1125356/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1501395/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1501395/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1150300/unique-tournament/11085/season/88715/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1150300/unique-tournament/11085/season/88715/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1094161/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1094161/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1477038/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1402519/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1805067/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1477038/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1402519/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1137753/unique-tournament/11085/season/88715/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1137753/unique-tournament/11085/season/88715/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1799505/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1613802/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1799505/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1467357/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1937442/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1805067/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1548134/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1200811/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1000261/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2083296/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2111754/unique-tournament/40/season/87925/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1548134/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1200811/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1149151/unique-tournament/205/season/77015/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1149151/unique-tournament/205/season/77015/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1000261/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1914975/unique-tournament/671/season/78576/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1914975/unique-tournament/671/season/78576/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2083296/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1613802/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1857382/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1487053/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1065160/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1467357/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1937442/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2111754/unique-tournament/40/season/87925/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2230864/unique-tournament/46/season/87924/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2230864/unique-tournament/46/season/87924/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1857382/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1487053/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1134558/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1134558/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1923313/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2001946/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1940450/unique-tournament/22/season/87867/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1065160/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1809093/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1931773/unique-tournament/20/season/87809/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1809093/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1931773/unique-tournament/20/season/87809/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1923313/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/2001946/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1940450/unique-tournament/22/season/87867/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1431611/unique-tournament/212/season/77283/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1431611/unique-tournament/212/season/77283/statistics/overall</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1432282/unique-tournament/11085/season/88715/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1432282/unique-tournament/11085/season/88715/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10550,8 +10841,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J521" totalsRowShown="0">
-  <autoFilter ref="A1:J521" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J527" totalsRowShown="0">
+  <autoFilter ref="A1:J527" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -10868,7 +11159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J521"/>
+  <dimension ref="A1:J527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -12045,6 +12336,8 @@
       <c r="H37" s="2" t="s">
         <v>1480</v>
       </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38">
@@ -12132,8 +12425,12 @@
       <c r="H40" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>3511</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41">
@@ -12189,8 +12486,12 @@
       <c r="H42" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+      <c r="I42" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>3513</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43">
@@ -12277,8 +12578,12 @@
       <c r="H45" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>3514</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>3515</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46">
@@ -12305,8 +12610,12 @@
       <c r="H46" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>3516</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>3517</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47">
@@ -12390,8 +12699,12 @@
       <c r="H49" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>3518</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>3521</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50">
@@ -12536,8 +12849,12 @@
       <c r="H54" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
+      <c r="I54" s="2" t="s">
+        <v>3519</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>3522</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55">
@@ -12647,8 +12964,12 @@
       <c r="H58" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
+      <c r="I58" s="2" t="s">
+        <v>3523</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>3524</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59">
@@ -17220,8 +17541,12 @@
       <c r="H207" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="I207" s="2"/>
-      <c r="J207" s="2"/>
+      <c r="I207" s="2" t="s">
+        <v>3525</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>3527</v>
+      </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208">
@@ -17544,8 +17869,12 @@
       <c r="H218" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="I218" s="2"/>
-      <c r="J218" s="2"/>
+      <c r="I218" s="2" t="s">
+        <v>3520</v>
+      </c>
+      <c r="J218" s="2" t="s">
+        <v>3530</v>
+      </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219">
@@ -18077,8 +18406,12 @@
       <c r="H236" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="I236" s="2"/>
-      <c r="J236" s="2"/>
+      <c r="I236" s="2" t="s">
+        <v>3531</v>
+      </c>
+      <c r="J236" s="2" t="s">
+        <v>3536</v>
+      </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237">
@@ -18137,8 +18470,12 @@
       <c r="H238" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
+      <c r="I238" s="2" t="s">
+        <v>3532</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>3537</v>
+      </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239">
@@ -18162,8 +18499,12 @@
       <c r="H239" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="I239" s="2"/>
-      <c r="J239" s="2"/>
+      <c r="I239" s="2" t="s">
+        <v>3538</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>3539</v>
+      </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240">
@@ -18274,8 +18615,12 @@
       <c r="H243" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="I243" s="2"/>
-      <c r="J243" s="2"/>
+      <c r="I243" s="2" t="s">
+        <v>3533</v>
+      </c>
+      <c r="J243" s="2" t="s">
+        <v>3540</v>
+      </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244">
@@ -18504,8 +18849,12 @@
       <c r="H251" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="I251" s="2"/>
-      <c r="J251" s="2"/>
+      <c r="I251" s="2" t="s">
+        <v>3541</v>
+      </c>
+      <c r="J251" s="2" t="s">
+        <v>3542</v>
+      </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252">
@@ -18648,8 +18997,12 @@
       <c r="H256" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="I256" s="2"/>
-      <c r="J256" s="2"/>
+      <c r="I256" s="2" t="s">
+        <v>3534</v>
+      </c>
+      <c r="J256" s="2" t="s">
+        <v>3543</v>
+      </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257">
@@ -18702,8 +19055,12 @@
       <c r="H258" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="I258" s="2"/>
-      <c r="J258" s="2"/>
+      <c r="I258" s="2" t="s">
+        <v>3526</v>
+      </c>
+      <c r="J258" s="2" t="s">
+        <v>3544</v>
+      </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259">
@@ -19512,8 +19869,12 @@
       <c r="H286" s="2" t="s">
         <v>1924</v>
       </c>
-      <c r="I286" s="2"/>
-      <c r="J286" s="2"/>
+      <c r="I286" s="2" t="s">
+        <v>3528</v>
+      </c>
+      <c r="J286" s="2" t="s">
+        <v>3548</v>
+      </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287">
@@ -19624,8 +19985,12 @@
       <c r="H290" s="2" t="s">
         <v>1954</v>
       </c>
-      <c r="I290" s="2"/>
-      <c r="J290" s="2"/>
+      <c r="I290" s="2" t="s">
+        <v>3529</v>
+      </c>
+      <c r="J290" s="2" t="s">
+        <v>3549</v>
+      </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291">
@@ -20037,8 +20402,12 @@
       <c r="H304" s="2" t="s">
         <v>2045</v>
       </c>
-      <c r="I304" s="2"/>
-      <c r="J304" s="2"/>
+      <c r="I304" s="2" t="s">
+        <v>3535</v>
+      </c>
+      <c r="J304" s="2" t="s">
+        <v>3550</v>
+      </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305">
@@ -20062,8 +20431,12 @@
       <c r="H305" s="2" t="s">
         <v>2050</v>
       </c>
-      <c r="I305" s="2"/>
-      <c r="J305" s="2"/>
+      <c r="I305" s="2" t="s">
+        <v>3551</v>
+      </c>
+      <c r="J305" s="2" t="s">
+        <v>3552</v>
+      </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306">
@@ -22161,8 +22534,12 @@
       <c r="H376" s="2" t="s">
         <v>2508</v>
       </c>
-      <c r="I376" s="2"/>
-      <c r="J376" s="2"/>
+      <c r="I376" s="2" t="s">
+        <v>3545</v>
+      </c>
+      <c r="J376" s="2" t="s">
+        <v>3553</v>
+      </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377">
@@ -22186,8 +22563,12 @@
       <c r="H377" s="2" t="s">
         <v>2513</v>
       </c>
-      <c r="I377" s="2"/>
-      <c r="J377" s="2"/>
+      <c r="I377" s="2" t="s">
+        <v>3546</v>
+      </c>
+      <c r="J377" s="2" t="s">
+        <v>3554</v>
+      </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378">
@@ -22300,8 +22681,12 @@
       <c r="H381" s="2" t="s">
         <v>2530</v>
       </c>
-      <c r="I381" s="2"/>
-      <c r="J381" s="2"/>
+      <c r="I381" s="2" t="s">
+        <v>3555</v>
+      </c>
+      <c r="J381" s="2" t="s">
+        <v>3556</v>
+      </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382">
@@ -22385,8 +22770,12 @@
       <c r="H384" s="2" t="s">
         <v>2543</v>
       </c>
-      <c r="I384" s="2"/>
-      <c r="J384" s="2"/>
+      <c r="I384" s="2" t="s">
+        <v>3547</v>
+      </c>
+      <c r="J384" s="2" t="s">
+        <v>3560</v>
+      </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385">
@@ -22410,8 +22799,12 @@
       <c r="H385" s="2" t="s">
         <v>2548</v>
       </c>
-      <c r="I385" s="2"/>
-      <c r="J385" s="2"/>
+      <c r="I385" s="2" t="s">
+        <v>3561</v>
+      </c>
+      <c r="J385" s="2" t="s">
+        <v>3563</v>
+      </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386">
@@ -22463,8 +22856,12 @@
       <c r="H387" s="2" t="s">
         <v>2558</v>
       </c>
-      <c r="I387" s="2"/>
-      <c r="J387" s="2"/>
+      <c r="I387" s="2" t="s">
+        <v>3562</v>
+      </c>
+      <c r="J387" s="2" t="s">
+        <v>3564</v>
+      </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388">
@@ -22491,8 +22888,12 @@
       <c r="H388" s="2" t="s">
         <v>2563</v>
       </c>
-      <c r="I388" s="2"/>
-      <c r="J388" s="2"/>
+      <c r="I388" s="2" t="s">
+        <v>3557</v>
+      </c>
+      <c r="J388" s="2" t="s">
+        <v>3565</v>
+      </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389">
@@ -22541,8 +22942,12 @@
       <c r="H390" s="2" t="s">
         <v>2573</v>
       </c>
-      <c r="I390" s="2"/>
-      <c r="J390" s="2"/>
+      <c r="I390" s="2" t="s">
+        <v>3558</v>
+      </c>
+      <c r="J390" s="2" t="s">
+        <v>3566</v>
+      </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391">
@@ -22566,8 +22971,12 @@
       <c r="H391" s="2" t="s">
         <v>2577</v>
       </c>
-      <c r="I391" s="2"/>
-      <c r="J391" s="2"/>
+      <c r="I391" s="2" t="s">
+        <v>3559</v>
+      </c>
+      <c r="J391" s="2" t="s">
+        <v>3567</v>
+      </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392">
@@ -23408,8 +23817,12 @@
       <c r="H420" s="2" t="s">
         <v>2765</v>
       </c>
-      <c r="I420" s="2"/>
-      <c r="J420" s="2"/>
+      <c r="I420" s="2" t="s">
+        <v>3568</v>
+      </c>
+      <c r="J420" s="2" t="s">
+        <v>3569</v>
+      </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A421">
@@ -24417,8 +24830,12 @@
       <c r="H454" s="2" t="s">
         <v>2978</v>
       </c>
-      <c r="I454" s="2"/>
-      <c r="J454" s="2"/>
+      <c r="I454" s="2" t="s">
+        <v>3570</v>
+      </c>
+      <c r="J454" s="2" t="s">
+        <v>3571</v>
+      </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A455">
@@ -26397,6 +26814,179 @@
       </c>
       <c r="J521" s="2" t="s">
         <v>3474</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A522">
+        <v>674</v>
+      </c>
+      <c r="B522" t="s">
+        <v>263</v>
+      </c>
+      <c r="C522" t="s">
+        <v>3475</v>
+      </c>
+      <c r="D522" t="s">
+        <v>6</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>3476</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>3477</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>3478</v>
+      </c>
+      <c r="I522" s="2" t="s">
+        <v>3479</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A523">
+        <v>675</v>
+      </c>
+      <c r="B523" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C523" t="s">
+        <v>3482</v>
+      </c>
+      <c r="D523" t="s">
+        <v>10</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>3483</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>3484</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>3485</v>
+      </c>
+      <c r="I523" s="2" t="s">
+        <v>3486</v>
+      </c>
+      <c r="J523" s="2" t="s">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A524">
+        <v>676</v>
+      </c>
+      <c r="B524" t="s">
+        <v>775</v>
+      </c>
+      <c r="C524" t="s">
+        <v>3488</v>
+      </c>
+      <c r="D524" t="s">
+        <v>127</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>3489</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>3490</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>3491</v>
+      </c>
+      <c r="I524" s="2"/>
+      <c r="J524" s="2"/>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A525">
+        <v>677</v>
+      </c>
+      <c r="B525" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C525" t="s">
+        <v>3492</v>
+      </c>
+      <c r="D525" t="s">
+        <v>6</v>
+      </c>
+      <c r="E525" t="s">
+        <v>10</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>3493</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>3494</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>3495</v>
+      </c>
+      <c r="I525" s="2" t="s">
+        <v>3496</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A526">
+        <v>678</v>
+      </c>
+      <c r="B526" t="s">
+        <v>530</v>
+      </c>
+      <c r="C526" t="s">
+        <v>3498</v>
+      </c>
+      <c r="D526" t="s">
+        <v>127</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>3499</v>
+      </c>
+      <c r="G526" s="2" t="s">
+        <v>3500</v>
+      </c>
+      <c r="H526" s="2" t="s">
+        <v>3501</v>
+      </c>
+      <c r="I526" s="2" t="s">
+        <v>3502</v>
+      </c>
+      <c r="J526" s="2" t="s">
+        <v>3503</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A527">
+        <v>679</v>
+      </c>
+      <c r="B527" t="s">
+        <v>61</v>
+      </c>
+      <c r="C527" t="s">
+        <v>3504</v>
+      </c>
+      <c r="D527" t="s">
+        <v>21</v>
+      </c>
+      <c r="F527" s="2" t="s">
+        <v>3505</v>
+      </c>
+      <c r="G527" s="2" t="s">
+        <v>3506</v>
+      </c>
+      <c r="H527" s="2" t="s">
+        <v>3507</v>
+      </c>
+      <c r="I527" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="J527" s="2" t="s">
+        <v>3509</v>
       </c>
     </row>
   </sheetData>
@@ -28685,11 +29275,101 @@
     <hyperlink ref="H521" r:id="rId2281" xr:uid="{FDB8B5EE-9686-443B-9CBD-875139726FFD}"/>
     <hyperlink ref="I521" r:id="rId2282" xr:uid="{60E642AA-04E8-4752-B0CD-699CC1C92B30}"/>
     <hyperlink ref="J521" r:id="rId2283" xr:uid="{12DD4329-0B4E-41AA-B7A1-C95725498A3B}"/>
+    <hyperlink ref="F522" r:id="rId2284" xr:uid="{DDE67750-9662-4E99-89DB-06A9A2076695}"/>
+    <hyperlink ref="G522" r:id="rId2285" xr:uid="{BA6CCBA4-74AE-4737-85EE-3CA7C14CCA38}"/>
+    <hyperlink ref="H522" r:id="rId2286" xr:uid="{0AE23EEB-FB5C-4D99-B9B4-D8C8A6A48268}"/>
+    <hyperlink ref="I522" r:id="rId2287" xr:uid="{70061C3F-B0E5-4864-BF3E-21065BD1A774}"/>
+    <hyperlink ref="J522" r:id="rId2288" xr:uid="{C31A4A7C-578B-4320-AE56-91294AB71214}"/>
+    <hyperlink ref="F523" r:id="rId2289" xr:uid="{3350B123-0924-4DFF-912A-A03296F878B9}"/>
+    <hyperlink ref="G523" r:id="rId2290" xr:uid="{AD657B89-FCDE-4419-913F-5FBDA50A0FEA}"/>
+    <hyperlink ref="H523" r:id="rId2291" xr:uid="{86FE864E-3D0D-4A2A-BA92-08043B64ED27}"/>
+    <hyperlink ref="I523" r:id="rId2292" xr:uid="{F65CEA51-6F0F-4FA5-89E7-1703B20BDC48}"/>
+    <hyperlink ref="J523" r:id="rId2293" xr:uid="{1D91860B-235F-48AE-8FE8-9B7262B5B1C8}"/>
+    <hyperlink ref="F524" r:id="rId2294" xr:uid="{7AC86562-995F-46A3-9976-F247060A26B3}"/>
+    <hyperlink ref="G524" r:id="rId2295" xr:uid="{7A58BF03-FF36-41F1-AC2F-ACE73782CC38}"/>
+    <hyperlink ref="H524" r:id="rId2296" xr:uid="{41D48398-B36A-430F-A668-32A4B035CD3A}"/>
+    <hyperlink ref="F525" r:id="rId2297" xr:uid="{5573FF53-7D92-406A-B57B-7669921E984D}"/>
+    <hyperlink ref="G525" r:id="rId2298" xr:uid="{89653B3F-3CF3-4C17-98D8-E91F97F8D42A}"/>
+    <hyperlink ref="H525" r:id="rId2299" xr:uid="{6B6F001A-204C-44F9-9024-44D1C0F0E4D7}"/>
+    <hyperlink ref="I525" r:id="rId2300" xr:uid="{BC0A1042-D750-4360-AADB-432B73E85FED}"/>
+    <hyperlink ref="J525" r:id="rId2301" xr:uid="{468ECDC8-F399-448F-80E8-0E3A07113A3C}"/>
+    <hyperlink ref="F526" r:id="rId2302" xr:uid="{BAA234E2-3919-4A28-B6C6-EC3D71A20325}"/>
+    <hyperlink ref="G526" r:id="rId2303" xr:uid="{2C6B4060-A7D2-4605-B9E3-62DDDF16E937}"/>
+    <hyperlink ref="H526" r:id="rId2304" xr:uid="{7F99E897-E325-420B-BA4E-81002D1024CB}"/>
+    <hyperlink ref="I526" r:id="rId2305" xr:uid="{11890C6E-C5F8-4E97-9341-2D4E730BF39A}"/>
+    <hyperlink ref="J526" r:id="rId2306" xr:uid="{29FC1595-60B4-4CE4-9447-9F3A9B281A5B}"/>
+    <hyperlink ref="F527" r:id="rId2307" xr:uid="{954A5ADA-CE9B-42C2-BBEE-32C4AF93C8CE}"/>
+    <hyperlink ref="G527" r:id="rId2308" xr:uid="{286A292F-1556-4D1D-B59C-817FA5DCD015}"/>
+    <hyperlink ref="H527" r:id="rId2309" xr:uid="{521508F1-26C1-46BF-9D3A-6FCAD95817AE}"/>
+    <hyperlink ref="I527" r:id="rId2310" xr:uid="{243D1AD8-B641-4C00-A9A3-5DC91E0AF98D}"/>
+    <hyperlink ref="J527" r:id="rId2311" xr:uid="{9B8148F0-4A7D-41C6-86A8-E09CC7991A89}"/>
+    <hyperlink ref="I40" r:id="rId2312" xr:uid="{E22280B2-1345-4988-9EAC-C59F60B01E3E}"/>
+    <hyperlink ref="I45" r:id="rId2313" xr:uid="{5FB9701B-2AD5-4DFB-9C21-7AE511971C21}"/>
+    <hyperlink ref="J45" r:id="rId2314" xr:uid="{C4830FEF-1E74-4460-A695-123031F88C92}"/>
+    <hyperlink ref="I42" r:id="rId2315" xr:uid="{6FE79BF5-AD5C-420C-B809-D495ED679EC3}"/>
+    <hyperlink ref="J42" r:id="rId2316" xr:uid="{837CD5A4-1B45-411C-8C10-FC9BBFD831FC}"/>
+    <hyperlink ref="J40" r:id="rId2317" xr:uid="{13AD4B92-F026-4829-A1B6-9DFB17FBF8B1}"/>
+    <hyperlink ref="I46" r:id="rId2318" xr:uid="{78AD177A-06A1-4725-8D5F-C6E1D214B61B}"/>
+    <hyperlink ref="J46" r:id="rId2319" xr:uid="{54ADD4F7-5279-468B-A3EE-6BF81B02A625}"/>
+    <hyperlink ref="I49" r:id="rId2320" xr:uid="{9AD9B203-6C0A-431F-908E-48C79A294D13}"/>
+    <hyperlink ref="J49" r:id="rId2321" xr:uid="{9D115B3A-8A37-4957-A1BE-D42015AE6344}"/>
+    <hyperlink ref="I54" r:id="rId2322" xr:uid="{9A0F4FAD-6448-4DD2-B9CF-02701D9FA87B}"/>
+    <hyperlink ref="J54" r:id="rId2323" xr:uid="{6750F784-4437-478A-B1A7-618E82280C9E}"/>
+    <hyperlink ref="I58" r:id="rId2324" xr:uid="{54EF5EDC-CBD6-4C04-B30A-B5094B10BE33}"/>
+    <hyperlink ref="J58" r:id="rId2325" xr:uid="{C70C393C-A3B2-49D3-858F-74C6B13112F3}"/>
+    <hyperlink ref="I207" r:id="rId2326" xr:uid="{42B9C34D-BA79-4D8C-A3CF-18A81BB7E7BD}"/>
+    <hyperlink ref="J207" r:id="rId2327" xr:uid="{B1DE97E2-0CB5-40A2-93F6-D975FCB18406}"/>
+    <hyperlink ref="I218" r:id="rId2328" xr:uid="{A0C6678E-4FF2-4195-B2CC-324E04F60E1E}"/>
+    <hyperlink ref="J218" r:id="rId2329" xr:uid="{3E41698C-3123-450B-8D39-19625F3E1630}"/>
+    <hyperlink ref="I236" r:id="rId2330" xr:uid="{68D10AE1-E277-44BC-8D15-A87AB65CCC37}"/>
+    <hyperlink ref="J236" r:id="rId2331" xr:uid="{4125C49C-BCA3-4726-A0FC-AD598F9F04A5}"/>
+    <hyperlink ref="I238" r:id="rId2332" xr:uid="{A3F2A3AE-A793-45FC-8020-133AC457DEB9}"/>
+    <hyperlink ref="J238" r:id="rId2333" xr:uid="{BCCAB96F-E8E9-45D2-8035-C18914AB466C}"/>
+    <hyperlink ref="I239" r:id="rId2334" xr:uid="{3E24618E-4A15-4A0C-94B4-16A0B04A547D}"/>
+    <hyperlink ref="J239" r:id="rId2335" xr:uid="{D75E0B97-D98E-49EF-9175-0C3AFBD54FF9}"/>
+    <hyperlink ref="I243" r:id="rId2336" xr:uid="{00B16BFA-E449-4B0F-AC66-E2828320B03F}"/>
+    <hyperlink ref="J243" r:id="rId2337" xr:uid="{F95A4725-5CB4-4F4B-AE08-C9AEC6BC8F51}"/>
+    <hyperlink ref="I251" r:id="rId2338" xr:uid="{DCF355C5-CFE5-4E83-AF20-432EC3972B5A}"/>
+    <hyperlink ref="J251" r:id="rId2339" xr:uid="{D4D38240-C06F-46AF-92DF-283F5FA65304}"/>
+    <hyperlink ref="I256" r:id="rId2340" xr:uid="{375DED4D-4F79-4E49-8119-BAD375985C9D}"/>
+    <hyperlink ref="J256" r:id="rId2341" xr:uid="{694007C4-B5B5-402A-A336-4C0BFCF1AC9D}"/>
+    <hyperlink ref="I258" r:id="rId2342" xr:uid="{D088BE37-B196-4427-995A-1D97706F4639}"/>
+    <hyperlink ref="J258" r:id="rId2343" xr:uid="{DDE6899D-DDCE-422C-85EB-3A062E0AA74F}"/>
+    <hyperlink ref="I286" r:id="rId2344" xr:uid="{E7C8EC33-A99E-4474-AEFA-9BFB5F2DA1BD}"/>
+    <hyperlink ref="J286" r:id="rId2345" xr:uid="{B334BBEE-9515-4EAB-B628-E72024067564}"/>
+    <hyperlink ref="I290" r:id="rId2346" xr:uid="{AAF4CA46-8586-4F95-A4D6-FD8F0B984FC5}"/>
+    <hyperlink ref="J290" r:id="rId2347" xr:uid="{53FF4309-3AC5-4805-81E9-E67B3A65E686}"/>
+    <hyperlink ref="I304" r:id="rId2348" xr:uid="{59AF9B0F-35F0-4E4B-8CD8-8C83A0436DA4}"/>
+    <hyperlink ref="J304" r:id="rId2349" xr:uid="{8FED633C-7874-4DC9-ADAE-361D1DB2826A}"/>
+    <hyperlink ref="I305" r:id="rId2350" xr:uid="{B6E99817-662C-4158-9579-5C12FAA6A8C8}"/>
+    <hyperlink ref="J305" r:id="rId2351" xr:uid="{091B456D-B1C1-40E1-9F8A-C3F876947F7B}"/>
+    <hyperlink ref="I376" r:id="rId2352" xr:uid="{B77B0DD5-93E4-44D5-8D22-626C275C1C7F}"/>
+    <hyperlink ref="J376" r:id="rId2353" xr:uid="{76E241F3-EF62-43EF-90F0-09DB131832D0}"/>
+    <hyperlink ref="I377" r:id="rId2354" xr:uid="{885C6DFA-0606-4CB4-8372-08EB2B787B1E}"/>
+    <hyperlink ref="J377" r:id="rId2355" xr:uid="{3BB01226-13CD-4912-AE80-25C62AA3A9BC}"/>
+    <hyperlink ref="I381" r:id="rId2356" xr:uid="{47EE5396-CE9B-4A65-836F-CED23F3B1CA8}"/>
+    <hyperlink ref="J381" r:id="rId2357" xr:uid="{524A7A4C-BF01-4C74-ACAA-5D2502AEFDA3}"/>
+    <hyperlink ref="I384" r:id="rId2358" xr:uid="{CC85524E-F71C-4FED-B112-20C35F6192C6}"/>
+    <hyperlink ref="J384" r:id="rId2359" xr:uid="{D7FDA165-E7CC-4520-90E9-B4EF609FAAE1}"/>
+    <hyperlink ref="I385" r:id="rId2360" xr:uid="{2E8D43AD-64B6-4D0A-99AB-FF818CB8A9D1}"/>
+    <hyperlink ref="J385" r:id="rId2361" xr:uid="{205E15BA-198B-4B8F-9392-157F552D4AB0}"/>
+    <hyperlink ref="I387" r:id="rId2362" xr:uid="{804971A5-C49D-4A8C-B7F5-0778EFABBA09}"/>
+    <hyperlink ref="J387" r:id="rId2363" xr:uid="{D507BA85-B8F7-42D9-B5D4-64DB5DAD27A1}"/>
+    <hyperlink ref="I388" r:id="rId2364" xr:uid="{BC04A1DF-3069-4116-8556-404398787858}"/>
+    <hyperlink ref="J388" r:id="rId2365" xr:uid="{EF77B5E9-A3A5-4ECE-9328-04646B951DD4}"/>
+    <hyperlink ref="I390" r:id="rId2366" xr:uid="{1E99C044-6827-4F3C-9072-CC1E2F628E60}"/>
+    <hyperlink ref="J390" r:id="rId2367" xr:uid="{9CF24713-0FF3-402E-8AC7-C71104DEFC83}"/>
+    <hyperlink ref="I391" r:id="rId2368" xr:uid="{4EB46E16-9944-4716-B544-78F50581AA95}"/>
+    <hyperlink ref="J391" r:id="rId2369" xr:uid="{A82D76CC-7812-4053-9D00-9B98BAB0F332}"/>
+    <hyperlink ref="I420" r:id="rId2370" xr:uid="{0751E19B-B28C-4973-B8D6-AE8E34B08674}"/>
+    <hyperlink ref="J420" r:id="rId2371" xr:uid="{8D28D182-1FFF-45D5-98D5-F35A90831F88}"/>
+    <hyperlink ref="I454" r:id="rId2372" xr:uid="{80A6AB6F-FA0B-4F0E-B256-B6A0D6C61B81}"/>
+    <hyperlink ref="J454" r:id="rId2373" xr:uid="{30B7406E-6193-4B6B-BAF5-EE46FAB1D265}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2284"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2374"/>
   <tableParts count="1">
-    <tablePart r:id="rId2285"/>
+    <tablePart r:id="rId2375"/>
   </tableParts>
 </worksheet>
 </file>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\data_scout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676533F5-9CB7-47EF-B0B9-979C2D5967F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4313D7BA-932C-493E-AD06-3FEB5166D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{74451770-FF53-415F-8FE2-EAFB6BA6C97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hráči" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4467" uniqueCount="3572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4475" uniqueCount="3579">
   <si>
     <t>id</t>
   </si>
@@ -10765,6 +10765,27 @@
   </si>
   <si>
     <t>https://www.sofascore.com/api/v1/player/1432282/unique-tournament/11085/season/88715/statistics/overall</t>
+  </si>
+  <si>
+    <t>Eetu</t>
+  </si>
+  <si>
+    <t>Turkki</t>
+  </si>
+  <si>
+    <t>https://www.transfermarkt.com/eetu-turkki/profil/spieler/1018031</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/en-us/football/player/eetu-turkki/1542038</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542038</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542038/unique-tournament/41/season/87930/ratings</t>
+  </si>
+  <si>
+    <t>https://www.sofascore.com/api/v1/player/1542038/unique-tournament/41/season/87930/statistics/overall</t>
   </si>
 </sst>
 </file>
@@ -10841,8 +10862,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J527" totalsRowShown="0">
-  <autoFilter ref="A1:J527" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}" name="Tabulka1" displayName="Tabulka1" ref="A1:J528" totalsRowShown="0">
+  <autoFilter ref="A1:J528" xr:uid="{1A3377AB-106B-4B39-9B7B-989296654869}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G173">
     <sortCondition ref="A1:A173"/>
   </sortState>
@@ -11159,7 +11180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716247E-1F35-4206-BB80-F74D5865F4AF}">
-  <dimension ref="A1:J527"/>
+  <dimension ref="A1:J528"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -26987,6 +27008,35 @@
       </c>
       <c r="J527" s="2" t="s">
         <v>3509</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A528">
+        <v>680</v>
+      </c>
+      <c r="B528" t="s">
+        <v>3572</v>
+      </c>
+      <c r="C528" t="s">
+        <v>3573</v>
+      </c>
+      <c r="D528" t="s">
+        <v>20</v>
+      </c>
+      <c r="F528" s="2" t="s">
+        <v>3574</v>
+      </c>
+      <c r="G528" s="2" t="s">
+        <v>3575</v>
+      </c>
+      <c r="H528" s="2" t="s">
+        <v>3576</v>
+      </c>
+      <c r="I528" s="2" t="s">
+        <v>3577</v>
+      </c>
+      <c r="J528" s="2" t="s">
+        <v>3578</v>
       </c>
     </row>
   </sheetData>
@@ -29365,11 +29415,16 @@
     <hyperlink ref="J420" r:id="rId2371" xr:uid="{8D28D182-1FFF-45D5-98D5-F35A90831F88}"/>
     <hyperlink ref="I454" r:id="rId2372" xr:uid="{80A6AB6F-FA0B-4F0E-B256-B6A0D6C61B81}"/>
     <hyperlink ref="J454" r:id="rId2373" xr:uid="{30B7406E-6193-4B6B-BAF5-EE46FAB1D265}"/>
+    <hyperlink ref="F528" r:id="rId2374" xr:uid="{457A6E37-E158-4E13-89D4-4FF095844F2C}"/>
+    <hyperlink ref="G528" r:id="rId2375" xr:uid="{32B36E69-B800-4670-BFA9-B64D5A276200}"/>
+    <hyperlink ref="H528" r:id="rId2376" xr:uid="{8BD199F3-C0DC-46C3-A17D-AABB75CFCB9B}"/>
+    <hyperlink ref="I528" r:id="rId2377" xr:uid="{E29A2C1D-506F-4318-8363-A40BAEBFA1D9}"/>
+    <hyperlink ref="J528" r:id="rId2378" xr:uid="{3760307F-0EF8-4EF8-9A16-C82D62B64EBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2374"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2379"/>
   <tableParts count="1">
-    <tablePart r:id="rId2375"/>
+    <tablePart r:id="rId2380"/>
   </tableParts>
 </worksheet>
 </file>
